--- a/reports/2026-03-20/summary_daily.xlsx
+++ b/reports/2026-03-20/summary_daily.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,33 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9EDF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +59,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,89 +459,289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>March 20 Fri</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total Sales:</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>24151.34</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>24151.34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>BEER</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>5879.6</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>5879.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>COOLCIDER</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>4209.67</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>4209.67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>487.2</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>487.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>120.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Rewards</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-155</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-155</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SPIRITS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>6033.3</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6033.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>WINE</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>511.98</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>511.98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>WINE RED</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2265.37</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2265.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>WINE WHITE</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1751.27</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1751.27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Net Total Sales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>21043.59</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>21043.59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GST 5%</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1037.43</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1037.43</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PST 7%</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>LIQ TAX 10%</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2065.97</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2065.97</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Total taxes</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>3107.75</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3107.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Total Sales</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B18" s="3" t="n">
         <v>24151.34</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>21043.59</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GST</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1037.43</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PST</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Liquor Tax</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2065.97</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v>24151.34</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B19" s="5" t="n">
         <v>712.8200000000001</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="C19" s="5" t="n">
+        <v>712.8200000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Customer count</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
         <v>594</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Average Sale</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>35.42691919191919</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>35.42691919191919</v>
       </c>
     </row>
   </sheetData>
